--- a/data/trans_camb/P1002-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,12</t>
+          <t>-2,39; 3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,01</t>
+          <t>-2,15; 3,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,89</t>
+          <t>-1,53; 3,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,15</t>
+          <t>-2,89; 5,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 3,68</t>
+          <t>-3,8; 3,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,37</t>
+          <t>-2,88; 4,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,09</t>
+          <t>-1,61; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,25</t>
+          <t>-1,89; 2,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,33</t>
+          <t>-0,77; 3,46</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,44; 127,22</t>
+          <t>-48,32; 134,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 118,54</t>
+          <t>-48,3; 115,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 172,25</t>
+          <t>-34,32; 142,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 118,44</t>
+          <t>-37,39; 124,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 83,74</t>
+          <t>-47,7; 84,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 121,63</t>
+          <t>-33,74; 104,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 89,18</t>
+          <t>-30,66; 84,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 69,39</t>
+          <t>-34,51; 69,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 96,92</t>
+          <t>-13,8; 98,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,31</t>
+          <t>-2,05; 4,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,21</t>
+          <t>-2,74; 3,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 1,36</t>
+          <t>-4,13; 1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 6,66</t>
+          <t>-1,72; 7,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 1,96</t>
+          <t>-5,31; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,94</t>
+          <t>-2,63; 4,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,44</t>
+          <t>-0,96; 4,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,52</t>
+          <t>-3,06; 1,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,99</t>
+          <t>-2,73; 1,85</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 196,1</t>
+          <t>-39,48; 213,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 153,6</t>
+          <t>-55,11; 153,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,62; 64,27</t>
+          <t>-73,17; 73,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 124,81</t>
+          <t>-21,68; 141,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 43,27</t>
+          <t>-60,64; 36,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 101,49</t>
+          <t>-29,1; 92,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 109,44</t>
+          <t>-16,71; 101,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,86; 38,99</t>
+          <t>-46,62; 44,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 49,75</t>
+          <t>-39,51; 45,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 6,27</t>
+          <t>0,26; 6,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,91</t>
+          <t>-2,02; 3,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 4,21</t>
+          <t>-4,55; 4,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 13,45</t>
+          <t>-0,47; 13,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 12,09</t>
+          <t>-2,81; 12,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 5,08</t>
+          <t>-6,89; 4,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 7,37</t>
+          <t>1,91; 7,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,65</t>
+          <t>-1,03; 4,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 3,49</t>
+          <t>-4,52; 3,41</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 166,67</t>
+          <t>1,55; 166,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 96,93</t>
+          <t>-32,39; 95,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 85,47</t>
+          <t>-64,41; 99,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 207,13</t>
+          <t>-4,68; 199,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 181,51</t>
+          <t>-26,23; 191,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,51; 83,45</t>
+          <t>-48,17; 71,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,23; 144,23</t>
+          <t>23,73; 151,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 93,38</t>
+          <t>-15,14; 94,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,21; 61,03</t>
+          <t>-59,81; 59,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,95</t>
+          <t>-0,49; 4,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,76</t>
+          <t>-3,13; 0,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,81</t>
+          <t>-2,25; 1,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,64</t>
+          <t>0,23; 6,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,75</t>
+          <t>-1,35; 4,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 0,58</t>
+          <t>-6,71; 0,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,18</t>
+          <t>0,52; 4,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,66</t>
+          <t>-1,5; 1,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,7</t>
+          <t>-3,4; 0,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 68,48</t>
+          <t>-6,18; 75,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 14,01</t>
+          <t>-40,26; 11,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 32,3</t>
+          <t>-29,36; 30,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 92,91</t>
+          <t>2,15; 96,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 67,4</t>
+          <t>-13,5; 67,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,21; 6,99</t>
+          <t>-64,1; 6,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 65,68</t>
+          <t>6,12; 61,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 25,01</t>
+          <t>-18,26; 24,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 10,31</t>
+          <t>-42,33; 8,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,08</t>
+          <t>-3,45; 3,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 4,38</t>
+          <t>-2,05; 5,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 5,35</t>
+          <t>-1,76; 5,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,06; 14,09</t>
+          <t>6,31; 14,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,48</t>
+          <t>1,96; 9,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 7,36</t>
+          <t>-0,45; 7,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,34</t>
+          <t>3,51; 8,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,25</t>
+          <t>1,01; 6,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,88</t>
+          <t>0,04; 5,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,94; 83,39</t>
+          <t>-44,05; 99,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 119,55</t>
+          <t>-27,18; 133,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 143,04</t>
+          <t>-22,56; 141,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53,15; 197,66</t>
+          <t>55,99; 196,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,93; 133,35</t>
+          <t>17,4; 137,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 99,33</t>
+          <t>-4,11; 105,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,45; 128,99</t>
+          <t>34,87; 143,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11,05; 97,9</t>
+          <t>10,38; 94,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,45; 96,11</t>
+          <t>0,4; 85,57</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,62</t>
+          <t>-2,32; 4,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,55</t>
+          <t>-2,64; 3,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 7,6</t>
+          <t>-2,19; 7,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,42</t>
+          <t>2,91; 8,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,98</t>
+          <t>-0,49; 4,78</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,9</t>
+          <t>2,56; 7,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,98</t>
+          <t>2,39; 6,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,99</t>
+          <t>-0,55; 3,95</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,05</t>
+          <t>1,41; 6,3</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 237,64</t>
+          <t>-52,09; 210,33</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 189,42</t>
+          <t>-57,16; 187,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 429,75</t>
+          <t>-55,11; 363,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26,43; 106,73</t>
+          <t>28,53; 106,09</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 63,75</t>
+          <t>-6,05; 59,31</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22,97; 99,13</t>
+          <t>23,46; 97,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,76; 100,38</t>
+          <t>27,22; 99,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 56,71</t>
+          <t>-6,7; 55,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16,59; 84,89</t>
+          <t>15,88; 89,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,63</t>
+          <t>0,25; 2,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,24</t>
+          <t>-0,92; 1,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,43</t>
+          <t>-1,25; 1,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,06</t>
+          <t>4,03; 7,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,93</t>
+          <t>0,87; 3,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,0</t>
+          <t>-0,55; 2,9</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,5</t>
+          <t>2,55; 4,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,16</t>
+          <t>0,25; 2,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,82</t>
+          <t>-0,43; 1,85</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,96; 58,52</t>
+          <t>4,75; 59,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 26,85</t>
+          <t>-15,87; 28,46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 30,34</t>
+          <t>-22,57; 28,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43,94; 89,83</t>
+          <t>44,58; 91,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,33; 49,0</t>
+          <t>9,63; 47,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 38,57</t>
+          <t>-5,54; 36,58</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,67; 71,56</t>
+          <t>35,3; 70,02</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,12; 33,94</t>
+          <t>3,47; 32,92</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 27,72</t>
+          <t>-5,64; 28,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1002-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,18</t>
+          <t>-2,26; 3,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,06</t>
+          <t>-2,65; 2,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,49</t>
+          <t>-1,58; 3,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 5,21</t>
+          <t>-2,61; 5,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,46</t>
+          <t>-3,78; 3,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 4,07</t>
+          <t>-2,47; 4,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,01</t>
+          <t>-1,38; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,27</t>
+          <t>-1,93; 2,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,46</t>
+          <t>-0,91; 3,16</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,32; 134,91</t>
+          <t>-51,86; 134,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 115,65</t>
+          <t>-53,53; 119,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 142,39</t>
+          <t>-33,6; 137,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,39; 124,55</t>
+          <t>-34,93; 139,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 84,18</t>
+          <t>-48,21; 100,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 104,52</t>
+          <t>-30,75; 120,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 84,73</t>
+          <t>-26,33; 86,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 69,21</t>
+          <t>-34,25; 67,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 98,56</t>
+          <t>-16,58; 89,81</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,33</t>
+          <t>-2,06; 4,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,28</t>
+          <t>-2,5; 3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,13</t>
+          <t>-3,73; 1,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 7,25</t>
+          <t>-2,09; 6,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 1,88</t>
+          <t>-5,58; 1,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,61</t>
+          <t>-2,64; 4,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,26</t>
+          <t>-0,85; 4,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,81</t>
+          <t>-3,09; 1,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,85</t>
+          <t>-2,36; 2,21</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-31,08%</t>
+          <t>-26,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-5,91%</t>
+          <t>-0,83%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 213,81</t>
+          <t>-40,72; 204,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 153,02</t>
+          <t>-49,39; 197,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,17; 73,3</t>
+          <t>-68,24; 102,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 141,0</t>
+          <t>-21,92; 125,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 36,6</t>
+          <t>-63,64; 39,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 92,67</t>
+          <t>-30,78; 95,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 101,34</t>
+          <t>-15,28; 102,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 44,6</t>
+          <t>-47,13; 54,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 45,79</t>
+          <t>-35,75; 55,65</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>2,72</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>2,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,6</t>
+          <t>0,08; 6,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,79</t>
+          <t>-1,94; 3,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,57</t>
+          <t>-0,42; 6,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 13,68</t>
+          <t>-0,28; 13,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 12,43</t>
+          <t>-2,86; 12,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 4,68</t>
+          <t>-6,81; 4,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,58</t>
+          <t>1,7; 7,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,62</t>
+          <t>-1,1; 4,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 3,41</t>
+          <t>-0,59; 4,83</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-6,1%</t>
+          <t>-4,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-1,45%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 166,71</t>
+          <t>-3,29; 157,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 95,37</t>
+          <t>-31,0; 105,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,41; 99,99</t>
+          <t>-11,67; 146,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 199,61</t>
+          <t>-6,99; 206,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 191,69</t>
+          <t>-21,56; 187,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,17; 71,04</t>
+          <t>-50,04; 77,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,73; 151,3</t>
+          <t>19,79; 145,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 94,64</t>
+          <t>-14,45; 94,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,81; 59,65</t>
+          <t>-7,97; 90,97</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-0,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,06</t>
+          <t>-0,46; 3,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,57</t>
+          <t>-3,15; 0,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,77</t>
+          <t>-2,13; 1,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,66</t>
+          <t>0,17; 6,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 4,38</t>
+          <t>-1,42; 4,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,57</t>
+          <t>-3,08; 2,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,01</t>
+          <t>0,61; 4,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,6</t>
+          <t>-1,61; 1,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,57</t>
+          <t>-1,95; 1,33</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-5,71%</t>
+          <t>-4,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-26,54%</t>
+          <t>-6,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,54%</t>
+          <t>-3,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 75,71</t>
+          <t>-7,09; 68,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 11,43</t>
+          <t>-41,51; 9,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 30,93</t>
+          <t>-29,03; 29,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 96,59</t>
+          <t>1,66; 94,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 67,12</t>
+          <t>-14,47; 64,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,1; 6,96</t>
+          <t>-28,99; 31,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,12; 61,5</t>
+          <t>7,89; 64,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 24,43</t>
+          <t>-19,31; 25,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 8,7</t>
+          <t>-23,59; 20,25</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,64</t>
+          <t>-3,44; 3,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 5,03</t>
+          <t>-2,13; 4,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,39</t>
+          <t>-2,63; 4,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,31; 14,17</t>
+          <t>6,44; 13,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,96; 9,7</t>
+          <t>2,15; 9,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 7,57</t>
+          <t>1,16; 7,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,95</t>
+          <t>3,39; 8,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,16</t>
+          <t>1,23; 6,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 5,61</t>
+          <t>0,84; 5,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 99,07</t>
+          <t>-43,71; 84,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 133,57</t>
+          <t>-26,43; 121,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 141,19</t>
+          <t>-32,62; 105,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55,99; 196,08</t>
+          <t>57,33; 190,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,4; 137,45</t>
+          <t>19,64; 122,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 105,56</t>
+          <t>8,98; 109,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,87; 143,7</t>
+          <t>36,6; 138,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10,38; 94,38</t>
+          <t>13,6; 93,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,4; 85,57</t>
+          <t>9,66; 84,27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,99</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>3,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,45</t>
+          <t>-2,22; 4,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,56</t>
+          <t>-2,68; 3,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 7,29</t>
+          <t>-1,71; 7,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,18</t>
+          <t>3,21; 8,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,78</t>
+          <t>-0,15; 4,75</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,81</t>
+          <t>2,34; 7,32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,79</t>
+          <t>2,42; 6,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,95</t>
+          <t>-0,4; 4,02</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,3</t>
+          <t>1,73; 6,37</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>49,63%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 210,33</t>
+          <t>-48,92; 212,68</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-57,16; 187,41</t>
+          <t>-59,67; 186,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 363,58</t>
+          <t>-45,99; 367,86</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28,53; 106,09</t>
+          <t>31,24; 104,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 59,31</t>
+          <t>-1,82; 58,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,46; 97,89</t>
+          <t>23,88; 92,15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,22; 99,97</t>
+          <t>25,91; 94,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 55,48</t>
+          <t>-5,04; 57,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15,88; 89,3</t>
+          <t>20,21; 89,1</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>1,38</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,67</t>
+          <t>0,25; 2,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,32</t>
+          <t>-1,05; 1,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,39</t>
+          <t>-0,54; 1,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,1</t>
+          <t>3,82; 6,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,72</t>
+          <t>0,85; 3,69</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,9</t>
+          <t>0,77; 3,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,42</t>
+          <t>2,5; 4,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,08</t>
+          <t>0,25; 2,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,85</t>
+          <t>0,49; 2,18</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>4,75; 59,37</t>
+          <t>4,01; 58,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 28,46</t>
+          <t>-17,78; 26,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 28,99</t>
+          <t>-9,21; 36,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>44,58; 91,8</t>
+          <t>41,31; 88,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,63; 47,52</t>
+          <t>9,22; 47,83</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 36,58</t>
+          <t>8,43; 45,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,3; 70,02</t>
+          <t>34,31; 70,16</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,47; 32,92</t>
+          <t>3,2; 33,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 28,33</t>
+          <t>6,38; 33,82</t>
         </is>
       </c>
     </row>
